--- a/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
+++ b/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b09a53443ec48a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Re1309acb51e24d6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R8e558cd3343842e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7559230dac87431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Rf9e6ba5170434506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R278efcbdf7084557"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -102,22 +102,19 @@
     <x:t xml:space="preserve">A user can ask a question and receive relevant passages with source entry and date citations.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Indexing pipeline is stable.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M018</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pass the five-question retrieval test</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Five real journal questions are scored for retrieval quality, citation accuracy, and appropriate refusal.</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Planned</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Indexing pipeline is stable.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Complete</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M018</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pass the five-question retrieval test</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Five real journal questions are scored for retrieval quality, citation accuracy, and appropriate refusal.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Natural-language retrieval is implemented.</x:t>
@@ -368,7 +365,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -403,6 +400,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF156082"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E7F9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -458,7 +460,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="47">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -598,6 +600,33 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="7" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="7" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -641,7 +670,7 @@
         <x:color rgb="FF2E6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -652,7 +681,7 @@
         <x:color rgb="FF2E6B3A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -663,7 +692,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -674,7 +703,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -1081,7 +1110,7 @@
         <x:v>Complete</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="96" customHeight="1">
       <x:c r="A3" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -1112,27 +1141,31 @@
       <x:c r="J3" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L3" s="16">
-        <x:v>0.0</x:v>
+      <x:c r="K3" s="13" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M3" s="17">
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="N3" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O3" s="18"/>
-      <x:c r="P3" s="18"/>
-      <x:c r="Q3" s="19" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O3" s="47" t="str">
+        <x:v>2026-08-21 • 47 tests passed • cited library retrieval and insufficient-evidence refusal verified • branch codex/m013-natural-language-retrieval</x:v>
+      </x:c>
+      <x:c r="P3" s="47" t="str">
+        <x:v>Codex reconciliation: M013 verified with synthetic journals only; no private content inspected. Next: approve transition to M018 and provide five private questions for local-only scoring.</x:v>
+      </x:c>
+      <x:c r="Q3" s="19" t="str">
+        <x:v>Complete</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
         <x:v>18</x:v>
@@ -1147,10 +1180,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G4" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H4" s="7">
         <x:v>46326.0</x:v>
@@ -1162,7 +1195,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K4" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L4" s="9">
         <x:v>0.0</x:v>
@@ -1171,17 +1204,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="O4" s="11"/>
       <x:c r="P4" s="11"/>
       <x:c r="Q4" s="20" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
         <x:v>18</x:v>
@@ -1196,10 +1229,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="G5" s="13" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="H5" s="15">
         <x:v>46356.0</x:v>
@@ -1211,7 +1244,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K5" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L5" s="16">
         <x:v>0.0</x:v>
@@ -1220,17 +1253,17 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N5" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="O5" s="18"/>
       <x:c r="P5" s="18"/>
       <x:c r="Q5" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
         <x:v>18</x:v>
@@ -1239,16 +1272,16 @@
         <x:v>46357.0</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="H6" s="7">
         <x:v>46387.0</x:v>
@@ -1260,7 +1293,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L6" s="9">
         <x:v>0.0</x:v>
@@ -1269,17 +1302,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N6" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O6" s="11"/>
       <x:c r="P6" s="11"/>
       <x:c r="Q6" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
         <x:v>18</x:v>
@@ -1288,16 +1321,16 @@
         <x:v>46388.0</x:v>
       </x:c>
       <x:c r="D7" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E7" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="G7" s="13" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="H7" s="15">
         <x:v>46418.0</x:v>
@@ -1309,7 +1342,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L7" s="16">
         <x:v>0.0</x:v>
@@ -1318,17 +1351,17 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N7" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O7" s="18"/>
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>18</x:v>
@@ -1337,28 +1370,28 @@
         <x:v>46419.0</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="H8" s="7">
         <x:v>46446.0</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L8" s="9">
         <x:v>0.0</x:v>
@@ -1367,17 +1400,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N8" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
       <x:c r="Q8" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
         <x:v>18</x:v>
@@ -1386,28 +1419,28 @@
         <x:v>46508.0</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46538.0</x:v>
       </x:c>
       <x:c r="I9" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J9" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L9" s="16">
         <x:v>0.0</x:v>
@@ -1416,47 +1449,47 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="N9" s="13" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="O9" s="18"/>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="6">
         <x:v>46539.0</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="H10" s="7">
         <x:v>46568.0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L10" s="9">
         <x:v>0.0</x:v>
@@ -1465,35 +1498,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N10" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
       <x:c r="Q10" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>46569.0</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="H11" s="15">
         <x:v>46599.0</x:v>
@@ -1502,10 +1535,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L11" s="16">
         <x:v>0.0</x:v>
@@ -1514,47 +1547,47 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N11" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="6">
         <x:v>46600.0</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E12" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="5" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="G12" s="5" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="H12" s="7">
         <x:v>46630.0</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L12" s="9">
         <x:v>0.0</x:v>
@@ -1563,47 +1596,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N12" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
       <x:c r="Q12" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C13" s="14">
         <x:v>46661.0</x:v>
       </x:c>
       <x:c r="D13" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G13" s="13" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="H13" s="15">
         <x:v>46691.0</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L13" s="16">
         <x:v>0.0</x:v>
@@ -1612,47 +1645,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N13" s="13" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="6">
         <x:v>46692.0</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="5" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G14" s="5" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G14" s="5" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="H14" s="7">
         <x:v>46721.0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K14" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L14" s="9">
         <x:v>0.0</x:v>
@@ -1661,47 +1694,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N14" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
       <x:c r="Q14" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>46722.0</x:v>
       </x:c>
       <x:c r="D15" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="H15" s="15">
         <x:v>46752.0</x:v>
       </x:c>
       <x:c r="I15" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K15" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L15" s="16">
         <x:v>0.0</x:v>
@@ -1710,47 +1743,47 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="N15" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
       <x:c r="Q15" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="6">
         <x:v>46784.0</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="5" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="G16" s="5" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="H16" s="7">
         <x:v>46812.0</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J16" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L16" s="9">
         <x:v>0.0</x:v>
@@ -1759,35 +1792,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N16" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
       <x:c r="Q16" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="14">
         <x:v>46813.0</x:v>
       </x:c>
       <x:c r="D17" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E17" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F17" s="13" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="H17" s="15">
         <x:v>46843.0</x:v>
@@ -1799,7 +1832,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K17" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L17" s="16">
         <x:v>0.0</x:v>
@@ -1808,12 +1841,12 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N17" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1834,7 +1867,7 @@
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
       <x:c r="Q18" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1855,7 +1888,7 @@
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1876,7 +1909,7 @@
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
       <x:c r="Q20" s="19" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1897,8 +1930,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123aa4f0b2b74d57"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eee95b6fa2b4565"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd048741ef78462a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeed95ca78d040f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1982,7 +2015,7 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="H2" s="41" t="str">
-        <x:v>Approve transition to the September milestone.</x:v>
+        <x:v>M013 transition approved and completed.</x:v>
       </x:c>
       <x:c r="I2" s="45" t="n">
         <x:v>46255</x:v>
@@ -1991,7 +2024,7 @@
         <x:v>38 tests passed; synthetic index created 3 chunks; query returned date/source/title/chunk; unchanged re-index skipped 3/3; commit 4e512f2.</x:v>
       </x:c>
       <x:c r="K2" s="41" t="str">
-        <x:v>Update AGENTS.md to the M013 scope when the user approves.</x:v>
+        <x:v>Completed; retained as M013 prerequisite evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="72" customHeight="1">
@@ -2011,22 +2044,26 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="E3" s="42" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="F3" s="42" t="str">
         <x:f>'Sheet1'!K3</x:f>
-        <x:v>Planned</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="G3" s="42" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="H3" s="42" t="str">
-        <x:v>Approve AGENTS.md scope transition and answer/refusal behavior.</x:v>
-      </x:c>
-      <x:c r="I3" s="46"/>
-      <x:c r="J3" s="42" t="str"/>
+        <x:v>Approve transition to M018 and provide five private questions for local-only scoring; do not place private content in this workbook.</x:v>
+      </x:c>
+      <x:c r="I3" s="46" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="J3" s="42" t="str">
+        <x:v>47 tests passed; natural-language CLI returned only the cited library passage; unrelated hash-collision candidates were filtered; a zero-evidence query returned no passage.</x:v>
+      </x:c>
       <x:c r="K3" s="42" t="str">
-        <x:v>Plan and implement natural-language retrieval with citations after the scope transition.</x:v>
+        <x:v>Prepare a privacy-safe offline five-question retrieval scoring harness after approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="72" customHeight="1">
@@ -2053,7 +2090,7 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="G4" s="42" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Awaiting Input</x:v>
       </x:c>
       <x:c r="H4" s="42" t="str">
         <x:v>Provide five private questions and score results locally; do not place private content in this workbook.</x:v>
@@ -2061,7 +2098,7 @@
       <x:c r="I4" s="46"/>
       <x:c r="J4" s="42" t="str"/>
       <x:c r="K4" s="42" t="str">
-        <x:v>Wait for M013; then build a privacy-safe offline five-question scoring harness.</x:v>
+        <x:v>Provide five private questions locally; then run the privacy-safe offline scoring harness.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
@@ -2536,7 +2573,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re75277a2d1754eb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a4ded5ddc04735"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2692,10 +2729,102 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="51" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B7" s="50" t="str">
+        <x:v>M013</x:v>
+      </x:c>
+      <x:c r="C7" s="50" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D7" s="50" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E7" s="50" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F7" s="50" t="str">
+        <x:v>Definition of done verified against code, tests, and synthetic CLI checks.</x:v>
+      </x:c>
+      <x:c r="G7" s="50" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="52" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B8" s="53" t="str">
+        <x:v>M013</x:v>
+      </x:c>
+      <x:c r="C8" s="53" t="str">
+        <x:v>Progress %</x:v>
+      </x:c>
+      <x:c r="D8" s="53" t="str">
+        <x:v>0%</x:v>
+      </x:c>
+      <x:c r="E8" s="53" t="str">
+        <x:v>100%</x:v>
+      </x:c>
+      <x:c r="F8" s="53" t="str">
+        <x:v>All cited retrieval and insufficient-evidence behavior verified.</x:v>
+      </x:c>
+      <x:c r="G8" s="53" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="51" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>M013</x:v>
+      </x:c>
+      <x:c r="C9" s="50" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+      <x:c r="D9" s="50" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E9" s="50" t="str">
+        <x:v>Verification recorded</x:v>
+      </x:c>
+      <x:c r="F9" s="50" t="str">
+        <x:v>47 tests; cited library retrieval; collision candidates filtered; zero-evidence query refused.</x:v>
+      </x:c>
+      <x:c r="G9" s="50" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="54" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B10" s="55" t="str">
+        <x:v>M013</x:v>
+      </x:c>
+      <x:c r="C10" s="55" t="str">
+        <x:v>Notes / Revision</x:v>
+      </x:c>
+      <x:c r="D10" s="55" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E10" s="55" t="str">
+        <x:v>Reconciliation note recorded</x:v>
+      </x:c>
+      <x:c r="F10" s="55" t="str">
+        <x:v>Synthetic samples only; no private journal content inspected.</x:v>
+      </x:c>
+      <x:c r="G10" s="55" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1333b40dae44386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f29c211e5994f23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
+++ b/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7559230dac87431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Rf9e6ba5170434506"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R278efcbdf7084557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ed6e91990104507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Ra5ecc041619a41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="Ra7ca5497c6494e0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -111,25 +111,19 @@
     <x:t xml:space="preserve">Pass the five-question retrieval test</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Five real journal questions are scored for retrieval quality, citation accuracy, and appropriate refusal.</x:t>
+    <x:t xml:space="preserve">Natural-language retrieval is implemented.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M021</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Stabilize MVP v0.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The MVP runs locally, includes insufficient-evidence refusal behavior, has a README, and is useful in repeated use.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Planned</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Natural-language retrieval is implemented.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Due Soon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M021</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Stabilize MVP v0.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The MVP runs locally, includes insufficient-evidence refusal behavior, has a README, and is useful in repeated use.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Five-question test findings are available.</x:t>
@@ -365,7 +359,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -400,6 +394,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF156082"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E7F9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -460,7 +464,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="64">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -627,6 +631,30 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="7" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="7" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1163,7 +1191,7 @@
         <x:v>Complete</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="112" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1182,39 +1210,43 @@
       <x:c r="F4" s="5" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G4" s="5" t="s">
+      <x:c r="G4" s="56" t="str">
+        <x:v>Five fictional sample-journal questions are scored for top-passage retrieval quality, citation accuracy, and appropriate refusal, with every criterion passing.</x:v>
+      </x:c>
+      <x:c r="H4" s="57">
+        <x:v>46326.0</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="L4" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M4" s="59">
+        <x:v>8.0</x:v>
+      </x:c>
+      <x:c r="N4" s="56" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H4" s="7">
-        <x:v>46326.0</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J4" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K4" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L4" s="9">
-        <x:v>0.0</x:v>
-      </x:c>
-      <x:c r="M4" s="10">
-        <x:v>8.0</x:v>
-      </x:c>
-      <x:c r="N4" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="O4" s="11"/>
-      <x:c r="P4" s="11"/>
-      <x:c r="Q4" s="20" t="s">
-        <x:v>36</x:v>
+      <x:c r="O4" s="21" t="str">
+        <x:v>2026-08-21 • 54 tests passed • sample scorecard 5/5 • retrieval 4/4 • citations 4/4 • refusals 1/1 • branch codex/m018-five-question-retrieval-test</x:v>
+      </x:c>
+      <x:c r="P4" s="21" t="str">
+        <x:v>Codex reconciliation: M018 verified using only fictional sample journals; no private content inspected. Real/private evaluation remains deferred. Next: approve transition to M021 stabilization.</x:v>
+      </x:c>
+      <x:c r="Q4" s="56" t="str">
+        <x:v>Complete</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="13" t="s">
         <x:v>18</x:v>
@@ -1229,10 +1261,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G5" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H5" s="15">
         <x:v>46356.0</x:v>
@@ -1244,7 +1276,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K5" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L5" s="16">
         <x:v>0.0</x:v>
@@ -1253,17 +1285,17 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N5" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="O5" s="18"/>
       <x:c r="P5" s="18"/>
       <x:c r="Q5" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
         <x:v>18</x:v>
@@ -1272,16 +1304,16 @@
         <x:v>46357.0</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G6" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H6" s="7">
         <x:v>46387.0</x:v>
@@ -1293,7 +1325,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L6" s="9">
         <x:v>0.0</x:v>
@@ -1302,17 +1334,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N6" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O6" s="11"/>
       <x:c r="P6" s="11"/>
       <x:c r="Q6" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
         <x:v>18</x:v>
@@ -1321,16 +1353,16 @@
         <x:v>46388.0</x:v>
       </x:c>
       <x:c r="D7" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E7" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G7" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H7" s="15">
         <x:v>46418.0</x:v>
@@ -1342,7 +1374,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L7" s="16">
         <x:v>0.0</x:v>
@@ -1351,17 +1383,17 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N7" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O7" s="18"/>
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>18</x:v>
@@ -1370,28 +1402,28 @@
         <x:v>46419.0</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G8" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H8" s="7">
         <x:v>46446.0</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L8" s="9">
         <x:v>0.0</x:v>
@@ -1400,17 +1432,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N8" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
       <x:c r="Q8" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
         <x:v>18</x:v>
@@ -1419,28 +1451,28 @@
         <x:v>46508.0</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G9" s="13" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46538.0</x:v>
       </x:c>
       <x:c r="I9" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J9" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L9" s="16">
         <x:v>0.0</x:v>
@@ -1449,47 +1481,47 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="N9" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="O9" s="18"/>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="6">
         <x:v>46539.0</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H10" s="7">
         <x:v>46568.0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L10" s="9">
         <x:v>0.0</x:v>
@@ -1498,35 +1530,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N10" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
       <x:c r="Q10" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>46569.0</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G11" s="13" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H11" s="15">
         <x:v>46599.0</x:v>
@@ -1535,10 +1567,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L11" s="16">
         <x:v>0.0</x:v>
@@ -1547,47 +1579,47 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N11" s="13" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="6">
         <x:v>46600.0</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E12" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H12" s="7">
         <x:v>46630.0</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L12" s="9">
         <x:v>0.0</x:v>
@@ -1596,47 +1628,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N12" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
       <x:c r="Q12" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="14">
         <x:v>46661.0</x:v>
       </x:c>
       <x:c r="D13" s="13" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G13" s="13" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H13" s="15">
         <x:v>46691.0</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L13" s="16">
         <x:v>0.0</x:v>
@@ -1645,47 +1677,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N13" s="13" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="6">
         <x:v>46692.0</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G14" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H14" s="7">
         <x:v>46721.0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K14" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L14" s="9">
         <x:v>0.0</x:v>
@@ -1694,47 +1726,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N14" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
       <x:c r="Q14" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>46722.0</x:v>
       </x:c>
       <x:c r="D15" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G15" s="13" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H15" s="15">
         <x:v>46752.0</x:v>
       </x:c>
       <x:c r="I15" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K15" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L15" s="16">
         <x:v>0.0</x:v>
@@ -1743,47 +1775,47 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="N15" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
       <x:c r="Q15" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C16" s="6">
         <x:v>46784.0</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G16" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H16" s="7">
         <x:v>46812.0</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J16" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L16" s="9">
         <x:v>0.0</x:v>
@@ -1792,35 +1824,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N16" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
       <x:c r="Q16" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C17" s="14">
         <x:v>46813.0</x:v>
       </x:c>
       <x:c r="D17" s="13" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E17" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F17" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G17" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H17" s="15">
         <x:v>46843.0</x:v>
@@ -1832,7 +1864,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K17" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L17" s="16">
         <x:v>0.0</x:v>
@@ -1841,12 +1873,12 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N17" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1867,7 +1899,7 @@
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
       <x:c r="Q18" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1888,7 +1920,7 @@
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1909,7 +1941,7 @@
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
       <x:c r="Q20" s="19" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1930,8 +1962,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd048741ef78462a"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeed95ca78d040f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60aa25bdee54347"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8029cd4ad5442bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2054,7 +2086,7 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="H3" s="42" t="str">
-        <x:v>Approve transition to M018 and provide five private questions for local-only scoring; do not place private content in this workbook.</x:v>
+        <x:v>M018 transition approved and completed using fictional sample journals.</x:v>
       </x:c>
       <x:c r="I3" s="46" t="n">
         <x:v>46255</x:v>
@@ -2063,7 +2095,7 @@
         <x:v>47 tests passed; natural-language CLI returned only the cited library passage; unrelated hash-collision candidates were filtered; a zero-evidence query returned no passage.</x:v>
       </x:c>
       <x:c r="K3" s="42" t="str">
-        <x:v>Prepare a privacy-safe offline five-question retrieval scoring harness after approval.</x:v>
+        <x:v>Completed; retained as M018 prerequisite evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="72" customHeight="1">
@@ -2080,25 +2112,29 @@
         <x:v>46296</x:v>
       </x:c>
       <x:c r="D4" s="42" t="str">
-        <x:v>Evaluation + human evidence</x:v>
+        <x:v>Evaluation</x:v>
       </x:c>
       <x:c r="E4" s="42" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="F4" s="42" t="str">
         <x:f>'Sheet1'!K4</x:f>
-        <x:v>Planned</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="G4" s="42" t="str">
-        <x:v>Awaiting Input</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="H4" s="42" t="str">
-        <x:v>Provide five private questions and score results locally; do not place private content in this workbook.</x:v>
-      </x:c>
-      <x:c r="I4" s="46"/>
-      <x:c r="J4" s="42" t="str"/>
+        <x:v>Approve transition to M021 stabilization; real/private journal evaluation remains deferred.</x:v>
+      </x:c>
+      <x:c r="I4" s="46" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="J4" s="42" t="str">
+        <x:v>54 tests passed; five fictional questions scored 5/5; retrieval 4/4; citations 4/4; refusal 1/1; the temporary index was removed after the run.</x:v>
+      </x:c>
       <x:c r="K4" s="42" t="str">
-        <x:v>Provide five private questions locally; then run the privacy-safe offline scoring harness.</x:v>
+        <x:v>Define M021 stabilization scope from the sample evaluation findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
@@ -2125,15 +2161,15 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="G5" s="42" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Awaiting Input</x:v>
       </x:c>
       <x:c r="H5" s="42" t="str">
-        <x:v>Confirm repeated-use usefulness after the five-question findings.</x:v>
+        <x:v>Approve M021 stabilization scope and the repeated-use evidence plan.</x:v>
       </x:c>
       <x:c r="I5" s="46"/>
       <x:c r="J5" s="42" t="str"/>
       <x:c r="K5" s="42" t="str">
-        <x:v>Use M018 findings to define stabilization work.</x:v>
+        <x:v>Review M018 findings and select the smallest stabilization work.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
@@ -2573,7 +2609,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a4ded5ddc04735"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2966996de374311"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2821,10 +2857,125 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="51" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B11" s="50" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="C11" s="50" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D11" s="50" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E11" s="50" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F11" s="50" t="str">
+        <x:v>Definition of done verified against code, tests, and the fictional sample scorecard.</x:v>
+      </x:c>
+      <x:c r="G11" s="50" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="62" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B12" s="63" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>Progress %</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>0%</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>100%</x:v>
+      </x:c>
+      <x:c r="F12" s="63" t="str">
+        <x:v>All five sample cases and every applicable criterion passed.</x:v>
+      </x:c>
+      <x:c r="G12" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="51" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B13" s="50" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="str">
+        <x:v>Definition of Done</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="str">
+        <x:v>Five real journal questions</x:v>
+      </x:c>
+      <x:c r="E13" s="50" t="str">
+        <x:v>Five fictional sample-journal questions</x:v>
+      </x:c>
+      <x:c r="F13" s="50" t="str">
+        <x:v>User requested M018 execution with sample journal entries.</x:v>
+      </x:c>
+      <x:c r="G13" s="50" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="A14" s="62" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B14" s="63" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>Verification recorded</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>54 tests; cases 5/5; retrieval 4/4; citations 4/4; refusals 1/1.</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="45" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B15" s="41" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="C15" s="41" t="str">
+        <x:v>Notes / Revision</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E15" s="41" t="str">
+        <x:v>Reconciliation note recorded</x:v>
+      </x:c>
+      <x:c r="F15" s="41" t="str">
+        <x:v>Synthetic samples only; no private journal content inspected.</x:v>
+      </x:c>
+      <x:c r="G15" s="41" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f29c211e5994f23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b63351340c400a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
+++ b/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ed6e91990104507"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Ra5ecc041619a41ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="Ra7ca5497c6494e0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25d1f535d20c46df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="R97ea037b56a94810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R540a98804a924a8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -120,31 +120,28 @@
     <x:t xml:space="preserve">Stabilize MVP v0.1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The MVP runs locally, includes insufficient-evidence refusal behavior, has a README, and is useful in repeated use.</x:t>
+    <x:t xml:space="preserve">Five-question test findings are available.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Consolidate</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Automate updates and document backups</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">New entries can be added through a repeatable command or workflow, and the data/index backup process is tested.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Planned</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Five-question test findings are available.</x:t>
+    <x:t xml:space="preserve">MVP v0.1 is stable.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Future</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M026</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Consolidate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Automate updates and document backups</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">New entries can be added through a repeatable command or workflow, and the data/index backup process is tested.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MVP v0.1 is stable.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M030</x:t>
@@ -464,7 +461,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="64">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -656,6 +653,24 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -810,7 +825,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Updated At"/>
     <x:tableColumn id="2" name="Milestone ID"/>
@@ -1244,7 +1259,7 @@
         <x:v>Complete</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="232.5" customHeight="1">
       <x:c r="A5" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -1263,39 +1278,43 @@
       <x:c r="F5" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G5" s="13" t="s">
+      <x:c r="G5" s="66" t="str">
+        <x:v>The MVP refreshes its local index, answers multiple fictional questions with extractive citations or refusal, documents the workflow, and skips unchanged chunks on a repeated run.</x:v>
+      </x:c>
+      <x:c r="H5" s="67">
+        <x:v>46356.0</x:v>
+      </x:c>
+      <x:c r="I5" s="66" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J5" s="66" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K5" s="66" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="L5" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M5" s="69">
+        <x:v>10.0</x:v>
+      </x:c>
+      <x:c r="N5" s="66" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H5" s="15">
-        <x:v>46356.0</x:v>
-      </x:c>
-      <x:c r="I5" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J5" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="L5" s="16">
-        <x:v>0.0</x:v>
-      </x:c>
-      <x:c r="M5" s="17">
-        <x:v>10.0</x:v>
-      </x:c>
-      <x:c r="N5" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="O5" s="18"/>
-      <x:c r="P5" s="18"/>
-      <x:c r="Q5" s="19" t="s">
-        <x:v>39</x:v>
+      <x:c r="O5" s="47" t="str">
+        <x:v>2026-08-21 • 60 tests passed • multi-question answer/citation/refusal verified • repeated run skipped 3/3 • branch codex/m021-stabilize-mvp</x:v>
+      </x:c>
+      <x:c r="P5" s="47" t="str">
+        <x:v>Codex reconciliation: M021 verified with fictional journals only; no private content inspected. Real-world adoption evidence remains deferred to M030. Next: approve M026 backup location and recovery expectations.</x:v>
+      </x:c>
+      <x:c r="Q5" s="66" t="str">
+        <x:v>Complete</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
         <x:v>18</x:v>
@@ -1304,16 +1323,16 @@
         <x:v>46357.0</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G6" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H6" s="7">
         <x:v>46387.0</x:v>
@@ -1325,7 +1344,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K6" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L6" s="9">
         <x:v>0.0</x:v>
@@ -1334,17 +1353,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="O6" s="11"/>
       <x:c r="P6" s="11"/>
       <x:c r="Q6" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
         <x:v>18</x:v>
@@ -1353,16 +1372,16 @@
         <x:v>46388.0</x:v>
       </x:c>
       <x:c r="D7" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E7" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G7" s="13" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="H7" s="15">
         <x:v>46418.0</x:v>
@@ -1374,7 +1393,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L7" s="16">
         <x:v>0.0</x:v>
@@ -1383,17 +1402,17 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N7" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="O7" s="18"/>
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>18</x:v>
@@ -1402,28 +1421,28 @@
         <x:v>46419.0</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H8" s="7">
         <x:v>46446.0</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L8" s="9">
         <x:v>0.0</x:v>
@@ -1432,17 +1451,17 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N8" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
       <x:c r="Q8" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
         <x:v>18</x:v>
@@ -1451,28 +1470,28 @@
         <x:v>46508.0</x:v>
       </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46538.0</x:v>
       </x:c>
       <x:c r="I9" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J9" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L9" s="16">
         <x:v>0.0</x:v>
@@ -1481,47 +1500,47 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="N9" s="13" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O9" s="18"/>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="6">
         <x:v>46539.0</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="H10" s="7">
         <x:v>46568.0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L10" s="9">
         <x:v>0.0</x:v>
@@ -1530,35 +1549,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N10" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
       <x:c r="Q10" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="14">
         <x:v>46569.0</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="H11" s="15">
         <x:v>46599.0</x:v>
@@ -1567,10 +1586,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L11" s="16">
         <x:v>0.0</x:v>
@@ -1579,47 +1598,47 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N11" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C12" s="6">
         <x:v>46600.0</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E12" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="5" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="G12" s="5" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="H12" s="7">
         <x:v>46630.0</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L12" s="9">
         <x:v>0.0</x:v>
@@ -1628,47 +1647,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N12" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
       <x:c r="Q12" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="14">
         <x:v>46661.0</x:v>
       </x:c>
       <x:c r="D13" s="13" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="G13" s="13" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="H13" s="15">
         <x:v>46691.0</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L13" s="16">
         <x:v>0.0</x:v>
@@ -1677,47 +1696,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N13" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="6">
         <x:v>46692.0</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="5" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G14" s="5" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="G14" s="5" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="H14" s="7">
         <x:v>46721.0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K14" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L14" s="9">
         <x:v>0.0</x:v>
@@ -1726,47 +1745,47 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N14" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
       <x:c r="Q14" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B15" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C15" s="14">
         <x:v>46722.0</x:v>
       </x:c>
       <x:c r="D15" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="H15" s="15">
         <x:v>46752.0</x:v>
       </x:c>
       <x:c r="I15" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K15" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L15" s="16">
         <x:v>0.0</x:v>
@@ -1775,47 +1794,47 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="N15" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
       <x:c r="Q15" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="6">
         <x:v>46784.0</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="5" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="G16" s="5" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="H16" s="7">
         <x:v>46812.0</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J16" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L16" s="9">
         <x:v>0.0</x:v>
@@ -1824,35 +1843,35 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="N16" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
       <x:c r="Q16" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B17" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="14">
         <x:v>46813.0</x:v>
       </x:c>
       <x:c r="D17" s="13" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E17" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F17" s="13" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="H17" s="15">
         <x:v>46843.0</x:v>
@@ -1864,7 +1883,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K17" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L17" s="16">
         <x:v>0.0</x:v>
@@ -1873,12 +1892,12 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="N17" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1899,7 +1918,7 @@
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
       <x:c r="Q18" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1920,7 +1939,7 @@
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1941,7 +1960,7 @@
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
       <x:c r="Q20" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1962,8 +1981,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60aa25bdee54347"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8029cd4ad5442bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc380d423ccbc4486"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda8dbba5b91d4aa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2125,7 +2144,7 @@
         <x:v>Verified</x:v>
       </x:c>
       <x:c r="H4" s="42" t="str">
-        <x:v>Approve transition to M021 stabilization; real/private journal evaluation remains deferred.</x:v>
+        <x:v>M021 transition approved and completed; real/private journal evaluation remains deferred.</x:v>
       </x:c>
       <x:c r="I4" s="46" t="n">
         <x:v>46255</x:v>
@@ -2134,7 +2153,7 @@
         <x:v>54 tests passed; five fictional questions scored 5/5; retrieval 4/4; citations 4/4; refusal 1/1; the temporary index was removed after the run.</x:v>
       </x:c>
       <x:c r="K4" s="42" t="str">
-        <x:v>Define M021 stabilization scope from the sample evaluation findings.</x:v>
+        <x:v>Completed; retained as M021 prerequisite evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
@@ -2154,22 +2173,26 @@
         <x:v>Engineering + adoption</x:v>
       </x:c>
       <x:c r="E5" s="42" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="F5" s="42" t="str">
         <x:f>'Sheet1'!K5</x:f>
-        <x:v>Planned</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="G5" s="42" t="str">
-        <x:v>Awaiting Input</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="H5" s="42" t="str">
-        <x:v>Approve M021 stabilization scope and the repeated-use evidence plan.</x:v>
-      </x:c>
-      <x:c r="I5" s="46"/>
-      <x:c r="J5" s="42" t="str"/>
+        <x:v>M021 stabilization scope approved and completed; private adoption evidence remains deferred to M030.</x:v>
+      </x:c>
+      <x:c r="I5" s="46" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="J5" s="42" t="str">
+        <x:v>60 tests passed; package-level command refreshed 3 fictional journals; returned cited answers; refused an unsupported question; repeated run skipped unchanged chunks 3/3.</x:v>
+      </x:c>
       <x:c r="K5" s="42" t="str">
-        <x:v>Review M018 findings and select the smallest stabilization work.</x:v>
+        <x:v>Completed; retained as M026 prerequisite evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
@@ -2196,7 +2219,7 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="G6" s="42" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Awaiting Input</x:v>
       </x:c>
       <x:c r="H6" s="42" t="str">
         <x:v>Approve backup location and recovery expectations.</x:v>
@@ -2204,7 +2227,7 @@
       <x:c r="I6" s="46"/>
       <x:c r="J6" s="42" t="str"/>
       <x:c r="K6" s="42" t="str">
-        <x:v>Wait for stable MVP v0.1; then design a repeatable update and backup workflow.</x:v>
+        <x:v>Approve backup location and recovery expectations, then implement M026.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
@@ -2609,7 +2632,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2966996de374311"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3066ddc8d34586"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2650,7 +2673,7 @@
         <x:v>Updated By</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="52" customHeight="1">
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="45" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2673,7 +2696,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="52" customHeight="1">
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="46" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2696,7 +2719,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="52" customHeight="1">
+    <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="46" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2719,7 +2742,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="52" customHeight="1">
+    <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="46" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2742,7 +2765,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="52" customHeight="1">
+    <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="46" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2765,7 +2788,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" customHeight="1">
+    <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="51" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2788,7 +2811,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="48" customHeight="1">
+    <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="52" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2811,7 +2834,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
+    <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="51" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2834,7 +2857,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
+    <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="54" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2857,7 +2880,7 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="52" customHeight="1">
+    <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="51" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2880,30 +2903,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="52" customHeight="1">
-      <x:c r="A12" s="62" t="n">
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="52" t="n">
         <x:v>46255</x:v>
       </x:c>
-      <x:c r="B12" s="63" t="str">
+      <x:c r="B12" s="53" t="str">
         <x:v>M018</x:v>
       </x:c>
-      <x:c r="C12" s="63" t="str">
+      <x:c r="C12" s="53" t="str">
         <x:v>Progress %</x:v>
       </x:c>
-      <x:c r="D12" s="63" t="str">
+      <x:c r="D12" s="53" t="str">
         <x:v>0%</x:v>
       </x:c>
-      <x:c r="E12" s="63" t="str">
+      <x:c r="E12" s="53" t="str">
         <x:v>100%</x:v>
       </x:c>
-      <x:c r="F12" s="63" t="str">
+      <x:c r="F12" s="53" t="str">
         <x:v>All five sample cases and every applicable criterion passed.</x:v>
       </x:c>
-      <x:c r="G12" s="63" t="str">
+      <x:c r="G12" s="53" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="52" customHeight="1">
+    <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="51" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2926,30 +2949,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="52" customHeight="1">
-      <x:c r="A14" s="62" t="n">
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="52" t="n">
         <x:v>46255</x:v>
       </x:c>
-      <x:c r="B14" s="63" t="str">
+      <x:c r="B14" s="53" t="str">
         <x:v>M018</x:v>
       </x:c>
-      <x:c r="C14" s="63" t="str">
+      <x:c r="C14" s="53" t="str">
         <x:v>Evidence / Link</x:v>
       </x:c>
-      <x:c r="D14" s="63" t="str">
+      <x:c r="D14" s="53" t="str">
         <x:v>Blank</x:v>
       </x:c>
-      <x:c r="E14" s="63" t="str">
+      <x:c r="E14" s="53" t="str">
         <x:v>Verification recorded</x:v>
       </x:c>
-      <x:c r="F14" s="63" t="str">
+      <x:c r="F14" s="53" t="str">
         <x:v>54 tests; cases 5/5; retrieval 4/4; citations 4/4; refusals 1/1.</x:v>
       </x:c>
-      <x:c r="G14" s="63" t="str">
+      <x:c r="G14" s="53" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="52" customHeight="1">
+    <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="45" t="n">
         <x:v>46255</x:v>
       </x:c>
@@ -2969,13 +2992,174 @@
         <x:v>Synthetic samples only; no private journal content inspected.</x:v>
       </x:c>
       <x:c r="G15" s="41" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B16" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C16" s="64" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D16" s="64" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E16" s="64" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F16" s="64" t="str">
+        <x:v>Stabilized local MVP behavior verified with fictional journals.</x:v>
+      </x:c>
+      <x:c r="G16" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B17" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C17" s="64" t="str">
+        <x:v>Progress %</x:v>
+      </x:c>
+      <x:c r="D17" s="64" t="str">
+        <x:v>0%</x:v>
+      </x:c>
+      <x:c r="E17" s="64" t="str">
+        <x:v>100%</x:v>
+      </x:c>
+      <x:c r="F17" s="64" t="str">
+        <x:v>All selected stabilization acceptance behavior passed.</x:v>
+      </x:c>
+      <x:c r="G17" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B18" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C18" s="64" t="str">
+        <x:v>Codex Readiness</x:v>
+      </x:c>
+      <x:c r="D18" s="64" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F18" s="64" t="str">
+        <x:v>User approved execution of the next milestone and pull-request creation.</x:v>
+      </x:c>
+      <x:c r="G18" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B19" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C19" s="64" t="str">
+        <x:v>Definition of Done</x:v>
+      </x:c>
+      <x:c r="D19" s="64" t="str">
+        <x:v>Subjective repeated-use usefulness</x:v>
+      </x:c>
+      <x:c r="E19" s="64" t="str">
+        <x:v>Automated fictional repeated-run acceptance</x:v>
+      </x:c>
+      <x:c r="F19" s="64" t="str">
+        <x:v>Privacy rules preclude inspecting real journals; real adoption evidence is deferred to M030.</x:v>
+      </x:c>
+      <x:c r="G19" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B20" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C20" s="64" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+      <x:c r="D20" s="64" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E20" s="64" t="str">
+        <x:v>Verification recorded</x:v>
+      </x:c>
+      <x:c r="F20" s="64" t="str">
+        <x:v>60 tests; cited answers; explicit refusal; repeat run skipped unchanged chunks 3/3.</x:v>
+      </x:c>
+      <x:c r="G20" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B21" s="64" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C21" s="64" t="str">
+        <x:v>Notes / Revision</x:v>
+      </x:c>
+      <x:c r="D21" s="64" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E21" s="64" t="str">
+        <x:v>Reconciliation note recorded</x:v>
+      </x:c>
+      <x:c r="F21" s="64" t="str">
+        <x:v>Synthetic samples only; no private journal content inspected.</x:v>
+      </x:c>
+      <x:c r="G21" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B22" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C22" s="64" t="str">
+        <x:v>Agent Status</x:v>
+      </x:c>
+      <x:c r="D22" s="64" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E22" s="64" t="str">
+        <x:v>Awaiting Input</x:v>
+      </x:c>
+      <x:c r="F22" s="64" t="str">
+        <x:v>M021 is complete; backup location and recovery expectations are now the next gate.</x:v>
+      </x:c>
+      <x:c r="G22" s="64" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b63351340c400a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfab9455bd9dc41dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
+++ b/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25d1f535d20c46df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="R97ea037b56a94810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R540a98804a924a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb136a7770e144732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Rb9506718c2c84f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R9b217e3823d54785"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -135,28 +135,28 @@
     <x:t xml:space="preserve">New entries can be added through a repeatable command or workflow, and the data/index backup process is tested.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">MVP v0.1 is stable.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M030</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Method Formation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Log usage and identify the top failure modes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">At least ten real uses are logged and the top three failure patterns are prioritized.</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Planned</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">MVP v0.1 is stable.</x:t>
+    <x:t xml:space="preserve">MVP is usable enough for repeated use.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Future</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M030</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Method Formation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Log usage and identify the top failure modes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">At least ten real uses are logged and the top three failure patterns are prioritized.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MVP is usable enough for repeated use.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M035</x:t>
@@ -825,7 +825,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Updated At"/>
     <x:tableColumn id="2" name="Milestone ID"/>
@@ -1312,7 +1312,7 @@
         <x:v>Complete</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="108" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="s">
         <x:v>37</x:v>
       </x:c>
@@ -1343,27 +1343,31 @@
       <x:c r="J6" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K6" s="5" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="L6" s="9">
-        <x:v>0.0</x:v>
+      <x:c r="K6" s="5" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="L6" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M6" s="10">
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N6" s="5" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="O6" s="11"/>
-      <x:c r="P6" s="11"/>
-      <x:c r="Q6" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O6" s="21" t="str">
+        <x:v>2026-08-21 • 69 tests passed • create/verify backup CLI verified • 5-file fictional snapshot checksum-verified • branch codex/m026-local-backups</x:v>
+      </x:c>
+      <x:c r="P6" s="21" t="str">
+        <x:v>Codex reconciliation: M026 verified with fictional journals and a synthetic SQLite index only; no private content inspected. Backup destination stays explicit at runtime; restore rehearsal remains M059. Next: collect ten real uses for M030 without logging journal content.</x:v>
+      </x:c>
+      <x:c r="Q6" s="20" t="str">
+        <x:v>Complete</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
         <x:v>18</x:v>
@@ -1372,16 +1376,16 @@
         <x:v>46388.0</x:v>
       </x:c>
       <x:c r="D7" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E7" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G7" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H7" s="15">
         <x:v>46418.0</x:v>
@@ -1393,7 +1397,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="16">
         <x:v>0.0</x:v>
@@ -1402,12 +1406,12 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="N7" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O7" s="18"/>
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1421,7 +1425,7 @@
         <x:v>46419.0</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
         <x:v>20</x:v>
@@ -1442,7 +1446,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" s="9">
         <x:v>0.0</x:v>
@@ -1456,7 +1460,7 @@
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
       <x:c r="Q8" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1491,7 +1495,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L9" s="16">
         <x:v>0.0</x:v>
@@ -1505,7 +1509,7 @@
       <x:c r="O9" s="18"/>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1540,7 +1544,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L10" s="9">
         <x:v>0.0</x:v>
@@ -1554,7 +1558,7 @@
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
       <x:c r="Q10" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1589,7 +1593,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L11" s="16">
         <x:v>0.0</x:v>
@@ -1603,7 +1607,7 @@
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1638,7 +1642,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L12" s="9">
         <x:v>0.0</x:v>
@@ -1652,7 +1656,7 @@
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
       <x:c r="Q12" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1687,7 +1691,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L13" s="16">
         <x:v>0.0</x:v>
@@ -1701,7 +1705,7 @@
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1736,7 +1740,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K14" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L14" s="9">
         <x:v>0.0</x:v>
@@ -1750,7 +1754,7 @@
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
       <x:c r="Q14" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1785,7 +1789,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K15" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L15" s="16">
         <x:v>0.0</x:v>
@@ -1799,7 +1803,7 @@
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
       <x:c r="Q15" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1834,7 +1838,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L16" s="9">
         <x:v>0.0</x:v>
@@ -1848,7 +1852,7 @@
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
       <x:c r="Q16" s="20" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1883,7 +1887,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K17" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L17" s="16">
         <x:v>0.0</x:v>
@@ -1897,7 +1901,7 @@
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1918,7 +1922,7 @@
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
       <x:c r="Q18" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1939,7 +1943,7 @@
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1960,7 +1964,7 @@
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
       <x:c r="Q20" s="19" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1981,8 +1985,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc380d423ccbc4486"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda8dbba5b91d4aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8061fd8366a94c2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40201ac78a254384"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2212,22 +2216,26 @@
         <x:v>Engineering + operations</x:v>
       </x:c>
       <x:c r="E6" s="42" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="F6" s="42" t="str">
         <x:f>'Sheet1'!K6</x:f>
-        <x:v>Planned</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="G6" s="42" t="str">
-        <x:v>Awaiting Input</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="H6" s="42" t="str">
-        <x:v>Approve backup location and recovery expectations.</x:v>
-      </x:c>
-      <x:c r="I6" s="46"/>
-      <x:c r="J6" s="42" t="str"/>
+        <x:v>Backup location remains an explicit runtime choice; restore rehearsal is deferred to M059.</x:v>
+      </x:c>
+      <x:c r="I6" s="46" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="J6" s="42" t="str">
+        <x:v>69 tests passed; create and verify commands installed; fictional five-file snapshot created and checksum-verified; overwrite, unsafe destination, corruption, invalid manifest, and invalid index cases tested.</x:v>
+      </x:c>
       <x:c r="K6" s="42" t="str">
-        <x:v>Approve backup location and recovery expectations, then implement M026.</x:v>
+        <x:v>Completed; M030 now requires ten real uses and non-sensitive failure categories.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
@@ -2254,7 +2262,7 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="G7" s="42" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Awaiting Evidence</x:v>
       </x:c>
       <x:c r="H7" s="42" t="str">
         <x:v>Complete at least ten real uses and record only non-sensitive failure categories.</x:v>
@@ -2632,7 +2640,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3066ddc8d34586"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95dfdb5b03c64db8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3156,10 +3164,194 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="24" hidden="0" customHeight="1">
+      <x:c r="A23" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B23" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C23" s="64" t="str">
+        <x:v>Agent Status</x:v>
+      </x:c>
+      <x:c r="D23" s="64" t="str">
+        <x:v>Awaiting Input</x:v>
+      </x:c>
+      <x:c r="E23" s="64" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F23" s="64" t="str">
+        <x:v>A fixed location was unnecessary: the destination is supplied explicitly for every local backup.</x:v>
+      </x:c>
+      <x:c r="G23" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B24" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C24" s="64" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D24" s="64" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E24" s="64" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F24" s="64" t="str">
+        <x:v>Definition of done verified against code, tests, and a fictional CLI smoke run.</x:v>
+      </x:c>
+      <x:c r="G24" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B25" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C25" s="64" t="str">
+        <x:v>Progress %</x:v>
+      </x:c>
+      <x:c r="D25" s="64" t="str">
+        <x:v>0%</x:v>
+      </x:c>
+      <x:c r="E25" s="64" t="str">
+        <x:v>100%</x:v>
+      </x:c>
+      <x:c r="F25" s="64" t="str">
+        <x:v>The repeatable update and local backup acceptance behavior passed.</x:v>
+      </x:c>
+      <x:c r="G25" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="24" hidden="0" customHeight="1">
+      <x:c r="A26" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B26" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C26" s="64" t="str">
+        <x:v>Codex Readiness</x:v>
+      </x:c>
+      <x:c r="D26" s="64" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="E26" s="64" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="F26" s="64" t="str">
+        <x:v>Runtime destination selection resolved the location gate without adding cloud storage.</x:v>
+      </x:c>
+      <x:c r="G26" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="24" hidden="0" customHeight="1">
+      <x:c r="A27" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B27" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C27" s="64" t="str">
+        <x:v>Definition of Done</x:v>
+      </x:c>
+      <x:c r="D27" s="64" t="str">
+        <x:v>Generic update and backup process</x:v>
+      </x:c>
+      <x:c r="E27" s="64" t="str">
+        <x:v>Verified repeatable update plus checksummed local snapshot</x:v>
+      </x:c>
+      <x:c r="F27" s="64" t="str">
+        <x:v>Journals and a consistent SQLite index copy were manifested and verified locally.</x:v>
+      </x:c>
+      <x:c r="G27" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" hidden="0" customHeight="1">
+      <x:c r="A28" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B28" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C28" s="64" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+      <x:c r="D28" s="64" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E28" s="64" t="str">
+        <x:v>Verification recorded</x:v>
+      </x:c>
+      <x:c r="F28" s="64" t="str">
+        <x:v>69 tests; create/verify CLI; five-file fictional snapshot; SHA-256 verification passed.</x:v>
+      </x:c>
+      <x:c r="G28" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" hidden="0" customHeight="1">
+      <x:c r="A29" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B29" s="64" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C29" s="64" t="str">
+        <x:v>Notes / Revision</x:v>
+      </x:c>
+      <x:c r="D29" s="64" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E29" s="64" t="str">
+        <x:v>Reconciliation note recorded</x:v>
+      </x:c>
+      <x:c r="F29" s="64" t="str">
+        <x:v>Synthetic data only; no private journal content inspected; restore rehearsal remains M059.</x:v>
+      </x:c>
+      <x:c r="G29" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="65" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B30" s="64" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C30" s="64" t="str">
+        <x:v>Agent Status</x:v>
+      </x:c>
+      <x:c r="D30" s="64" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E30" s="64" t="str">
+        <x:v>Awaiting Evidence</x:v>
+      </x:c>
+      <x:c r="F30" s="64" t="str">
+        <x:v>M030 requires ten real uses and only non-sensitive failure categories.</x:v>
+      </x:c>
+      <x:c r="G30" s="64" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfab9455bd9dc41dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab6e83ec63642ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
+++ b/outputs/01a02405-eff6-71d0-a35b-93798c214f10/Second Mind Milestones.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb136a7770e144732"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="Rb9506718c2c84f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R9b217e3823d54785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd0be26250dda4002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex Execution" sheetId="2" r:id="R3ea9f550eae5437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="3" r:id="R96237e6a4fd64461"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -150,28 +150,28 @@
     <x:t xml:space="preserve">At least ten real uses are logged and the top three failure patterns are prioritized.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">MVP is usable enough for repeated use.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M035</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ship v0.2 fixes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The top retrieval or usability failures from the usage log are fixed and retested.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Support</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Planned</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">MVP is usable enough for repeated use.</x:t>
+    <x:t xml:space="preserve">Failure-mode priorities are clear.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Future</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M035</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ship v0.2 fixes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The top retrieval or usability failures from the usage log are fixed and retested.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Support</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Failure-mode priorities are clear.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M047</x:t>
@@ -461,7 +461,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="70">
+  <x:cellXfs count="74">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -671,6 +671,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -825,7 +837,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UpdateLogTable" displayName="UpdateLogTable" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Updated At"/>
     <x:tableColumn id="2" name="Milestone ID"/>
@@ -1365,58 +1377,62 @@
         <x:v>Complete</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="13" t="s">
+    <x:row r="7" ht="72" hidden="0" customHeight="1">
+      <x:c r="A7" s="66" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="66" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C7" s="14">
+      <x:c r="C7" s="70">
         <x:v>46388.0</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="D7" s="66" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="E7" s="66" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="F7" s="66" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="G7" s="66" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H7" s="15">
+      <x:c r="H7" s="67">
         <x:v>46418.0</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="I7" s="66" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="J7" s="66" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="K7" s="66" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="L7" s="68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="69">
+        <x:v>5.0</x:v>
+      </x:c>
+      <x:c r="N7" s="66" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L7" s="16">
-        <x:v>0.0</x:v>
-      </x:c>
-      <x:c r="M7" s="17">
-        <x:v>5.0</x:v>
-      </x:c>
-      <x:c r="N7" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O7" s="18"/>
-      <x:c r="P7" s="18"/>
-      <x:c r="Q7" s="19" t="s">
-        <x:v>48</x:v>
+      <x:c r="O7" s="47" t="str">
+        <x:v>2026-08-21 • 78 tests passed • privacy-safe local outcome logger/report verified • branch codex/m030-usage-evidence</x:v>
+      </x:c>
+      <x:c r="P7" s="47" t="str">
+        <x:v>Codex reconciliation: M030 tooling is ready and stores only a fixed category plus UTC timestamp. Real-use evidence remains 0/10; no journal content was inspected or logged.</x:v>
+      </x:c>
+      <x:c r="Q7" s="66" t="str">
+        <x:v>On Track</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>18</x:v>
@@ -1431,22 +1447,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G8" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H8" s="7">
         <x:v>46446.0</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L8" s="9">
         <x:v>0.0</x:v>
@@ -1455,12 +1471,12 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="N8" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
       <x:c r="Q8" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1489,13 +1505,13 @@
         <x:v>46538.0</x:v>
       </x:c>
       <x:c r="I9" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J9" s="13" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K9" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L9" s="16">
         <x:v>0.0</x:v>
@@ -1509,7 +1525,7 @@
       <x:c r="O9" s="18"/>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1538,13 +1554,13 @@
         <x:v>46568.0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L10" s="9">
         <x:v>0.0</x:v>
@@ -1558,7 +1574,7 @@
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
       <x:c r="Q10" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1593,7 +1609,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K11" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L11" s="16">
         <x:v>0.0</x:v>
@@ -1607,7 +1623,7 @@
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1636,13 +1652,13 @@
         <x:v>46630.0</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L12" s="9">
         <x:v>0.0</x:v>
@@ -1656,7 +1672,7 @@
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
       <x:c r="Q12" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1685,13 +1701,13 @@
         <x:v>46691.0</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K13" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L13" s="16">
         <x:v>0.0</x:v>
@@ -1705,7 +1721,7 @@
       <x:c r="O13" s="18"/>
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1734,13 +1750,13 @@
         <x:v>46721.0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K14" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L14" s="9">
         <x:v>0.0</x:v>
@@ -1754,7 +1770,7 @@
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
       <x:c r="Q14" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1783,13 +1799,13 @@
         <x:v>46752.0</x:v>
       </x:c>
       <x:c r="I15" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K15" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L15" s="16">
         <x:v>0.0</x:v>
@@ -1803,7 +1819,7 @@
       <x:c r="O15" s="18"/>
       <x:c r="P15" s="18"/>
       <x:c r="Q15" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1832,13 +1848,13 @@
         <x:v>46812.0</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J16" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K16" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L16" s="9">
         <x:v>0.0</x:v>
@@ -1852,7 +1868,7 @@
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
       <x:c r="Q16" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1887,7 +1903,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K17" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L17" s="16">
         <x:v>0.0</x:v>
@@ -1901,7 +1917,7 @@
       <x:c r="O17" s="18"/>
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1922,7 +1938,7 @@
       <x:c r="O18" s="18"/>
       <x:c r="P18" s="18"/>
       <x:c r="Q18" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1943,7 +1959,7 @@
       <x:c r="O19" s="18"/>
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1964,7 +1980,7 @@
       <x:c r="O20" s="18"/>
       <x:c r="P20" s="18"/>
       <x:c r="Q20" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1985,8 +2001,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8061fd8366a94c2d"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40201ac78a254384"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f31ba3841de43b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94c32786ed484d40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2238,7 +2254,7 @@
         <x:v>Completed; M030 now requires ten real uses and non-sensitive failure categories.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
       <x:c r="A7" s="42" t="str">
         <x:f>'Sheet1'!A7</x:f>
         <x:v>M030</x:v>
@@ -2258,19 +2274,22 @@
         <x:v>Time-gated</x:v>
       </x:c>
       <x:c r="F7" s="42" t="str">
-        <x:f>'Sheet1'!K7</x:f>
-        <x:v>Planned</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G7" s="42" t="str">
         <x:v>Awaiting Evidence</x:v>
       </x:c>
       <x:c r="H7" s="42" t="str">
-        <x:v>Complete at least ten real uses and record only non-sensitive failure categories.</x:v>
-      </x:c>
-      <x:c r="I7" s="46"/>
-      <x:c r="J7" s="42" t="str"/>
+        <x:v>Record one fixed, non-sensitive outcome category after each of ten real uses; never copy a question, answer, citation, source path, or journal text.</x:v>
+      </x:c>
+      <x:c r="I7" s="46" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="J7" s="42" t="str">
+        <x:v>78 tests passed; installed usage command verified; strict JSONL schema stores only version, UTC timestamp, and category; unexpected fields are rejected.</x:v>
+      </x:c>
       <x:c r="K7" s="42" t="str">
-        <x:v>Collect real usage before prioritizing failure modes.</x:v>
+        <x:v>Run ten real uses locally, record each outcome, then rerun the report to lock the top three failure priorities.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
@@ -2640,7 +2659,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95dfdb5b03c64db8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra025818b74ac4626"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3348,10 +3367,125 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="A31" s="72" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B31" s="73" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C31" s="73" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D31" s="73" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E31" s="73" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="F31" s="73" t="str">
+        <x:v>Privacy-safe usage-evidence tooling is implemented and verified; real-use evidence is still required.</x:v>
+      </x:c>
+      <x:c r="G31" s="73" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="72" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B32" s="73" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C32" s="73" t="str">
+        <x:v>Roadmap Status</x:v>
+      </x:c>
+      <x:c r="D32" s="73" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="E32" s="73" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="F32" s="73" t="str">
+        <x:v>The logger and deterministic top-three report are ready for local use.</x:v>
+      </x:c>
+      <x:c r="G32" s="73" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" hidden="0" customHeight="1">
+      <x:c r="A33" s="72" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B33" s="73" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C33" s="73" t="str">
+        <x:v>Privacy Control</x:v>
+      </x:c>
+      <x:c r="D33" s="73" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E33" s="73" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F33" s="73" t="str">
+        <x:v>The local schema accepts only version, UTC timestamp, and one fixed category; extra fields are rejected.</x:v>
+      </x:c>
+      <x:c r="G33" s="73" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" hidden="0" customHeight="1">
+      <x:c r="A34" s="72" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B34" s="73" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C34" s="73" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+      <x:c r="D34" s="73" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="E34" s="73" t="str">
+        <x:v>Verification recorded</x:v>
+      </x:c>
+      <x:c r="F34" s="73" t="str">
+        <x:v>78 tests passed; installed CLI smoke test passed; branch codex/m030-usage-evidence.</x:v>
+      </x:c>
+      <x:c r="G34" s="73" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="24" hidden="0" customHeight="1">
+      <x:c r="A35" s="72" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B35" s="73" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C35" s="73" t="str">
+        <x:v>Human Gate</x:v>
+      </x:c>
+      <x:c r="D35" s="73" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E35" s="73" t="str">
+        <x:v>0/10 real uses</x:v>
+      </x:c>
+      <x:c r="F35" s="73" t="str">
+        <x:v>Milestone completion requires ten real outcomes before the top three failure patterns can be finalized.</x:v>
+      </x:c>
+      <x:c r="G35" s="73" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab6e83ec63642ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb25f37caa77745f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>